--- a/Models/Птицы/results/Птица - Результаты прогнозов Prophet средние.xlsx
+++ b/Models/Птицы/results/Птица - Результаты прогнозов Prophet средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1296.38</v>
+        <v>1552.82</v>
       </c>
       <c r="C2" t="n">
-        <v>1087.96</v>
+        <v>1388.72</v>
       </c>
       <c r="D2" t="n">
-        <v>10.53</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>39.21</v>
+        <v>38.72</v>
       </c>
       <c r="C3" t="n">
-        <v>33.55</v>
+        <v>28.84</v>
       </c>
       <c r="D3" t="n">
-        <v>208.73</v>
+        <v>143.7</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1693.22</v>
+        <v>1313.43</v>
       </c>
       <c r="C4" t="n">
-        <v>1545.61</v>
+        <v>1198.79</v>
       </c>
       <c r="D4" t="n">
-        <v>13.17</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="5">
@@ -505,10 +505,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.44</v>
+        <v>0.39</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>0.23</v>
       </c>
       <c r="D5" t="inlineStr"/>
     </row>
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>564.6900000000001</v>
+        <v>848.14</v>
       </c>
       <c r="C6" t="n">
-        <v>519.04</v>
+        <v>729.8200000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>8.529999999999999</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="7">
@@ -541,7 +541,7 @@
         <v>0.1</v>
       </c>
       <c r="D7" t="n">
-        <v>99.98999999999999</v>
+        <v>99.95</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="D8" t="inlineStr"/>
     </row>
@@ -565,13 +565,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78.38</v>
+        <v>33.23</v>
       </c>
       <c r="C9" t="n">
-        <v>62.99</v>
+        <v>30.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1075.22</v>
+        <v>673.22</v>
       </c>
     </row>
     <row r="10">
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>451.89</v>
+        <v>694.34</v>
       </c>
       <c r="C10" t="n">
-        <v>391.54</v>
+        <v>643.1</v>
       </c>
       <c r="D10" t="n">
-        <v>23.15</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="11">
@@ -597,13 +597,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>335.36</v>
+        <v>344.6</v>
       </c>
       <c r="C11" t="n">
-        <v>270.03</v>
+        <v>304.67</v>
       </c>
       <c r="D11" t="n">
-        <v>27.94</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="12">
@@ -613,13 +613,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155.33</v>
+        <v>120.28</v>
       </c>
       <c r="C12" t="n">
-        <v>122.69</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>11.82</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -629,13 +629,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>365.51</v>
+        <v>261.29</v>
       </c>
       <c r="C13" t="n">
-        <v>306.67</v>
+        <v>210.83</v>
       </c>
       <c r="D13" t="n">
-        <v>36.41</v>
+        <v>15.23</v>
       </c>
     </row>
     <row r="14">
@@ -645,13 +645,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8.869999999999999</v>
+        <v>8.75</v>
       </c>
       <c r="C14" t="n">
-        <v>7.42</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>170.89</v>
+        <v>210.69</v>
       </c>
     </row>
     <row r="15">
@@ -661,13 +661,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>130951.84</v>
+        <v>166337.41</v>
       </c>
       <c r="C15" t="n">
-        <v>81476.91</v>
+        <v>119876.29</v>
       </c>
       <c r="D15" t="n">
-        <v>18483.84</v>
+        <v>22915.51</v>
       </c>
     </row>
     <row r="16">
@@ -677,13 +677,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>296.85</v>
+        <v>254.23</v>
       </c>
       <c r="C16" t="n">
-        <v>254.85</v>
+        <v>228.58</v>
       </c>
       <c r="D16" t="n">
-        <v>13.46</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="17">
@@ -693,13 +693,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>296.37</v>
+        <v>263.53</v>
       </c>
       <c r="C17" t="n">
-        <v>206.8</v>
+        <v>170.66</v>
       </c>
       <c r="D17" t="n">
-        <v>288.27</v>
+        <v>275.58</v>
       </c>
     </row>
     <row r="18">
@@ -709,10 +709,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>7889.28</v>
+        <v>483337.79</v>
       </c>
       <c r="C18" t="n">
-        <v>4573.55</v>
+        <v>279056.55</v>
       </c>
       <c r="D18" t="inlineStr"/>
     </row>
@@ -723,13 +723,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>206.15</v>
+        <v>244.4</v>
       </c>
       <c r="C19" t="n">
-        <v>197.52</v>
+        <v>213.54</v>
       </c>
       <c r="D19" t="n">
-        <v>91.48999999999999</v>
+        <v>60.6</v>
       </c>
     </row>
     <row r="20">
@@ -739,13 +739,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>153.28</v>
+        <v>331.96</v>
       </c>
       <c r="C20" t="n">
-        <v>131.16</v>
+        <v>314.94</v>
       </c>
       <c r="D20" t="n">
-        <v>93.5</v>
+        <v>52.94</v>
       </c>
     </row>
     <row r="21">
@@ -755,13 +755,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>332.24</v>
+        <v>264.25</v>
       </c>
       <c r="C21" t="n">
-        <v>280.98</v>
+        <v>232.66</v>
       </c>
       <c r="D21" t="n">
-        <v>40.34</v>
+        <v>31.45</v>
       </c>
     </row>
   </sheetData>
